--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3150</x:v>
+        <x:v>3690</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>15541</x:v>
+        <x:v>17041</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3150</x:v>
+        <x:v>3690</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>11168</x:v>
+        <x:v>11564</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>17821</x:v>
+        <x:v>19501</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>501</x:v>
+        <x:v>581</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>501</x:v>
+        <x:v>581</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2419,7 +2419,7 @@
       <x:c r="N34" s="56" t="s"/>
       <x:c r="O34" s="58" t="s"/>
       <x:c r="P34" s="60" t="n">
-        <x:v>1300</x:v>
+        <x:v>1960</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>951</x:v>
+        <x:v>1101</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2605,7 +2605,7 @@
       <x:c r="N42" s="56" t="s"/>
       <x:c r="O42" s="58" t="s"/>
       <x:c r="P42" s="60" t="n">
-        <x:v>100</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3541</x:v>
+        <x:v>3871</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>127346</x:v>
+        <x:v>132992</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>19501</x:v>
+        <x:v>20101</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2419,7 +2419,7 @@
       <x:c r="N34" s="56" t="s"/>
       <x:c r="O34" s="58" t="s"/>
       <x:c r="P34" s="60" t="n">
-        <x:v>1960</x:v>
+        <x:v>2200</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3871</x:v>
+        <x:v>3931</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>132992</x:v>
+        <x:v>133652</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3690</x:v>
+        <x:v>3150</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>66721</x:v>
+        <x:v>67441</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>17041</x:v>
+        <x:v>15541</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3690</x:v>
+        <x:v>3150</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>11564</x:v>
+        <x:v>11168</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>20101</x:v>
+        <x:v>18121</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>581</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>581</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2419,7 +2419,7 @@
       <x:c r="N34" s="56" t="s"/>
       <x:c r="O34" s="58" t="s"/>
       <x:c r="P34" s="60" t="n">
-        <x:v>2200</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>1101</x:v>
+        <x:v>951</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2605,7 +2605,7 @@
       <x:c r="N42" s="56" t="s"/>
       <x:c r="O42" s="58" t="s"/>
       <x:c r="P42" s="60" t="n">
-        <x:v>150</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3931</x:v>
+        <x:v>3631</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>133652</x:v>
+        <x:v>128456</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3150</x:v>
+        <x:v>3220</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3150</x:v>
+        <x:v>3220</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>18121</x:v>
+        <x:v>19381</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>501</x:v>
+        <x:v>641</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>501</x:v>
+        <x:v>641</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3631</x:v>
+        <x:v>3841</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>128456</x:v>
+        <x:v>130346</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>15541</x:v>
+        <x:v>17701</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>11168</x:v>
+        <x:v>21968</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3841</x:v>
+        <x:v>3871</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>130346</x:v>
+        <x:v>143336</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3220</x:v>
+        <x:v>3720</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2067,7 +2067,7 @@
       <x:c r="N19" s="56" t="s"/>
       <x:c r="O19" s="58" t="s"/>
       <x:c r="P19" s="60" t="n">
-        <x:v>0</x:v>
+        <x:v>1140</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>67441</x:v>
+        <x:v>69601</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>17701</x:v>
+        <x:v>29221</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3220</x:v>
+        <x:v>3720</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>21968</x:v>
+        <x:v>70568</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>19381</x:v>
+        <x:v>19981</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>641</x:v>
+        <x:v>841</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>641</x:v>
+        <x:v>841</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3871</x:v>
+        <x:v>4351</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>143336</x:v>
+        <x:v>209236</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>69601</x:v>
+        <x:v>70921</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>29221</x:v>
+        <x:v>29701</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4351</x:v>
+        <x:v>4381</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>209236</x:v>
+        <x:v>211066</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3720</x:v>
+        <x:v>3730</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3720</x:v>
+        <x:v>3730</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>19981</x:v>
+        <x:v>20161</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>841</x:v>
+        <x:v>861</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>841</x:v>
+        <x:v>861</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4381</x:v>
+        <x:v>4411</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>211066</x:v>
+        <x:v>211336</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3730</x:v>
+        <x:v>3740</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3730</x:v>
+        <x:v>3740</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>20161</x:v>
+        <x:v>20221</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>861</x:v>
+        <x:v>881</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>861</x:v>
+        <x:v>881</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4411</x:v>
+        <x:v>4441</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>211336</x:v>
+        <x:v>211486</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4441</x:v>
+        <x:v>4471</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>211486</x:v>
+        <x:v>211516</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>2900</x:v>
+        <x:v>3380</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3740</x:v>
+        <x:v>4640</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>29701</x:v>
+        <x:v>30421</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3740</x:v>
+        <x:v>4640</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4471</x:v>
+        <x:v>4531</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>211516</x:v>
+        <x:v>214576</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>4640</x:v>
+        <x:v>4700</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>4640</x:v>
+        <x:v>4700</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>20221</x:v>
+        <x:v>21301</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>881</x:v>
+        <x:v>1001</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>881</x:v>
+        <x:v>1001</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4531</x:v>
+        <x:v>4711</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>214576</x:v>
+        <x:v>216196</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>4700</x:v>
+        <x:v>4820</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>4700</x:v>
+        <x:v>4820</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>21301</x:v>
+        <x:v>23461</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>1001</x:v>
+        <x:v>1241</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>1001</x:v>
+        <x:v>1241</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4711</x:v>
+        <x:v>5071</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>216196</x:v>
+        <x:v>219436</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>4820</x:v>
+        <x:v>6820</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>30421</x:v>
+        <x:v>36421</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>4820</x:v>
+        <x:v>6820</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5071</x:v>
+        <x:v>5191</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>219436</x:v>
+        <x:v>229556</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>3380</x:v>
+        <x:v>3764</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>6820</x:v>
+        <x:v>7540</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>70921</x:v>
+        <x:v>72361</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>6820</x:v>
+        <x:v>7540</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23461</x:v>
+        <x:v>23641</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5191</x:v>
+        <x:v>5281</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>229556</x:v>
+        <x:v>233090</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>36421</x:v>
+        <x:v>37921</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5281</x:v>
+        <x:v>5311</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>233090</x:v>
+        <x:v>234620</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>37921</x:v>
+        <x:v>40141</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5311</x:v>
+        <x:v>5371</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>234620</x:v>
+        <x:v>236900</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23641</x:v>
+        <x:v>23821</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5371</x:v>
+        <x:v>5401</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>236900</x:v>
+        <x:v>237110</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>7540</x:v>
+        <x:v>7720</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>7540</x:v>
+        <x:v>7720</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>237110</x:v>
+        <x:v>237470</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>7720</x:v>
+        <x:v>7900</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2067,7 +2067,7 @@
       <x:c r="N19" s="56" t="s"/>
       <x:c r="O19" s="58" t="s"/>
       <x:c r="P19" s="60" t="n">
-        <x:v>1140</x:v>
+        <x:v>1620</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>40141</x:v>
+        <x:v>40621</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>7720</x:v>
+        <x:v>7900</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2485,7 +2485,7 @@
       <x:c r="N37" s="56" t="s"/>
       <x:c r="O37" s="58" t="s"/>
       <x:c r="P37" s="60" t="n">
-        <x:v>1</x:v>
+        <x:v>3001</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5401</x:v>
+        <x:v>5461</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>237470</x:v>
+        <x:v>241850</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23821</x:v>
+        <x:v>24001</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5461</x:v>
+        <x:v>5491</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>241850</x:v>
+        <x:v>242060</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24001</x:v>
+        <x:v>24181</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5491</x:v>
+        <x:v>5671</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>242060</x:v>
+        <x:v>242420</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24181</x:v>
+        <x:v>24361</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>242420</x:v>
+        <x:v>242600</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>72361</x:v>
+        <x:v>73561</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5671</x:v>
+        <x:v>5761</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>242600</x:v>
+        <x:v>243890</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>73561</x:v>
+        <x:v>76321</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>5761</x:v>
+        <x:v>6001</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>243890</x:v>
+        <x:v>246890</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>76321</x:v>
+        <x:v>84001</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6001</x:v>
+        <x:v>6241</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>246890</x:v>
+        <x:v>254810</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24361</x:v>
+        <x:v>24541</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6241</x:v>
+        <x:v>6271</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>254810</x:v>
+        <x:v>255020</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XIII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XIII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>7900</x:v>
+        <x:v>8400</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>40621</x:v>
+        <x:v>46621</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>7900</x:v>
+        <x:v>8400</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>6271</x:v>
+        <x:v>6421</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>255020</x:v>
+        <x:v>262170</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">
